--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
@@ -941,7 +941,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>attribution_method</t>
         </is>
       </c>
       <c r="B1" s="1" t="n">

--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
@@ -528,6 +528,102 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -601,7 +697,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -911,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1011,278 +1107,278 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>c3f</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="D2" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8768472906403941</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.8731527093596059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8682266009852216</v>
       </c>
       <c r="G2" t="n">
         <v>0.8448275862068966</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.833743842364532</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8238916256157636</v>
       </c>
       <c r="J2" t="n">
-        <v>0.791871921182266</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.8017241379310345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7697044334975369</v>
+        <v>0.770935960591133</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7549261083743842</v>
+        <v>0.7512315270935961</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7339901477832512</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7278325123152709</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7130541871921182</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6711822660098522</v>
       </c>
       <c r="S2" t="n">
-        <v>0.645320197044335</v>
+        <v>0.6477832512315271</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.6083743842364532</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5578817733990148</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.7783251231527094</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7315270935960592</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6810344827586207</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T3" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5369458128078818</v>
+        <v>0.5775862068965517</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="E4" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="F4" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="H4" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="I4" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8817733990147784</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="K4" t="n">
-        <v>0.875615763546798</v>
+        <v>0.7955665024630542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8608374384236454</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.7684729064039408</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8226600985221675</v>
+        <v>0.7401477832512315</v>
       </c>
       <c r="O4" t="n">
-        <v>0.812807881773399</v>
+        <v>0.7179802955665024</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.6847290640394089</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.6761083743842364</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.6477832512315271</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6650246305418719</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.5911330049261084</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5443349753694581</v>
+        <v>0.5751231527093597</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8509852216748769</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8300492610837439</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8103448275862069</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.791871921182266</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.7697044334975369</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.7549261083743842</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7943349753694581</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.7278325123152709</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7327586206896551</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.645320197044335</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6108374384236454</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5591133004926109</v>
+        <v>0.5529556650246306</v>
       </c>
       <c r="V5" t="n">
         <v>0.4655172413793103</v>
@@ -1291,7 +1387,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1301,58 +1397,58 @@
         <v>0.9088669950738916</v>
       </c>
       <c r="D6" t="n">
-        <v>0.919950738916256</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="E6" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.9113300492610836</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.9051724137931034</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="K6" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8115763546798029</v>
+        <v>0.8423645320197044</v>
       </c>
       <c r="N6" t="n">
+        <v>0.8349753694581281</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.8004926108374384</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.7660098522167488</v>
-      </c>
       <c r="P6" t="n">
-        <v>0.7352216748768473</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7315270935960592</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6748768472906403</v>
+        <v>0.6958128078817734</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6440886699507389</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.604679802955665</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5332512315270936</v>
+        <v>0.5369458128078818</v>
       </c>
       <c r="V6" t="n">
         <v>0.4655172413793103</v>
@@ -1361,17 +1457,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D7" t="n">
-        <v>0.919950738916256</v>
+        <v>0.9174876847290639</v>
       </c>
       <c r="E7" t="n">
         <v>0.916256157635468</v>
@@ -1380,49 +1476,49 @@
         <v>0.916256157635468</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9027093596059114</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="H7" t="n">
-        <v>0.895320197044335</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8731527093596059</v>
+        <v>0.8817733990147784</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8608374384236454</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8312807881773399</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8054187192118226</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7820197044334976</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7573891625615764</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="R7" t="n">
-        <v>0.708128078817734</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6650246305418719</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5997536945812808</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.5443349753694581</v>
       </c>
       <c r="V7" t="n">
         <v>0.4655172413793103</v>
@@ -1431,68 +1527,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D8" t="n">
         <v>0.8780788177339901</v>
       </c>
       <c r="E8" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8312807881773399</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.8509852216748769</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="J8" t="n">
+        <v>0.8423645320197044</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8325123152709359</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8091133004926109</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7943349753694581</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7746305418719212</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7327586206896551</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.7167487684729064</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.6970443349753694</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6834975369458128</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.6773399014778325</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
+        <v>0.6958128078817734</v>
+      </c>
+      <c r="S8" t="n">
         <v>0.6625615763546798</v>
       </c>
-      <c r="P8" t="n">
-        <v>0.6502463054187192</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.6182266009852216</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.604679802955665</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.5862068965517241</v>
-      </c>
       <c r="T8" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.6108374384236454</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5258620689655172</v>
+        <v>0.5591133004926109</v>
       </c>
       <c r="V8" t="n">
         <v>0.4655172413793103</v>
@@ -1501,68 +1597,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9261083743842364</v>
+        <v>0.919950738916256</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9248768472906403</v>
+        <v>0.9113300492610836</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8990147783251231</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8399014778325123</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8288177339901478</v>
+        <v>0.8115763546798029</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7967980295566502</v>
+        <v>0.7660098522167488</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7352216748768473</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7364532019704434</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6748768472906403</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6440886699507389</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5849753694581281</v>
+        <v>0.5874384236453202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5123152709359606</v>
+        <v>0.5332512315270936</v>
       </c>
       <c r="V9" t="n">
         <v>0.4655172413793103</v>
@@ -1571,68 +1667,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9261083743842364</v>
+        <v>0.919950738916256</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F10" t="n">
         <v>0.916256157635468</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9039408866995072</v>
+        <v>0.9027093596059114</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.895320197044335</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8768472906403941</v>
+        <v>0.8731527093596059</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="M10" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8362068965517241</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8066502463054187</v>
+        <v>0.8054187192118226</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7832512315270936</v>
+        <v>0.7820197044334976</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7598522167487685</v>
+        <v>0.7573891625615764</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6096059113300493</v>
+        <v>0.5997536945812808</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5443349753694581</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="V10" t="n">
         <v>0.4655172413793103</v>
@@ -1641,68 +1737,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>smoothgrad</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="G11" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7869458128078818</v>
+        <v>0.6834975369458128</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.6773399014778325</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7118226600985221</v>
+        <v>0.6502463054187192</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.6182266009852216</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6600985221674877</v>
+        <v>0.604679802955665</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5972906403940886</v>
+        <v>0.5529556650246306</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5566502463054187</v>
+        <v>0.5258620689655172</v>
       </c>
       <c r="V11" t="n">
         <v>0.4655172413793103</v>
@@ -1711,70 +1807,280 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9261083743842364</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9248768472906403</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8990147783251231</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8854679802955665</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8633004926108374</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8497536945812808</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.8288177339901478</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8201970443349754</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7967980295566502</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7733990147783252</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7364532019704434</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6514778325123153</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.5849753694581281</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.5123152709359606</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9261083743842364</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9174876847290639</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9039408866995072</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9002463054187192</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8768472906403941</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8854679802955665</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8694581280788177</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.854679802955665</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8362068965517241</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.8066502463054187</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7832512315270936</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7598522167487685</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.7204433497536946</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6674876847290641</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6096059113300493</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5443349753694581</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>smoothgrad</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8916256157635468</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8916256157635468</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.875615763546798</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8694581280788177</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8472906403940886</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8300492610837439</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8201970443349754</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8091133004926109</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7869458128078818</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7610837438423645</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7463054187192119</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.7118226600985221</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.6859605911330049</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6600985221674877</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6293103448275862</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.5972906403940886</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.5566502463054187</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B15" t="n">
         <v>0.9064039408866996</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C15" t="n">
         <v>0.915024630541872</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
         <v>0.9064039408866996</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E15" t="n">
         <v>0.9039408866995072</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F15" t="n">
         <v>0.8854679802955665</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G15" t="n">
         <v>0.8706896551724138</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H15" t="n">
         <v>0.8633004926108374</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I15" t="n">
         <v>0.8435960591133005</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J15" t="n">
         <v>0.8300492610837439</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K15" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L15" t="n">
         <v>0.7820197044334976</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M15" t="n">
         <v>0.7610837438423645</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N15" t="n">
         <v>0.7524630541871922</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O15" t="n">
         <v>0.7401477832512315</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P15" t="n">
         <v>0.7204433497536946</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q15" t="n">
         <v>0.6995073891625616</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R15" t="n">
         <v>0.6834975369458128</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S15" t="n">
         <v>0.6539408866995073</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T15" t="n">
         <v>0.6071428571428571</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U15" t="n">
         <v>0.5480295566502463</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V15" t="n">
         <v>0.4655172413793103</v>
       </c>
     </row>

--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
@@ -624,6 +624,198 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$16:$V$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$17:$V$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="16"/>
+          <order val="16"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$18:$V$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="17"/>
+          <order val="17"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$19:$V$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$20:$V$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -697,7 +889,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1007,10 +1199,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1177,7 +1369,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1190,55 +1382,55 @@
         <v>0.896551724137931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8596059113300493</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8263546798029556</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.7992610837438424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8041871921182266</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7783251231527094</v>
+        <v>0.7549261083743842</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7450738916256158</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7093596059113301</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6810344827586207</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6391625615763546</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.625615763546798</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5775862068965517</v>
+        <v>0.5615763546798029</v>
       </c>
       <c r="V3" t="n">
         <v>0.4667487684729064</v>
@@ -1247,68 +1439,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.9064039408866996</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.8866995073891626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="F4" t="n">
+        <v>0.8842364532019704</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8559113300492611</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8485221674876847</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.8472906403940886</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.8460591133004927</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8325123152709359</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8263546798029556</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.812807881773399</v>
-      </c>
       <c r="K4" t="n">
-        <v>0.7955665024630542</v>
+        <v>0.8189655172413793</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7684729064039408</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7401477832512315</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7179802955665024</v>
+        <v>0.7376847290640394</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6847290640394089</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6761083743842364</v>
+        <v>0.687192118226601</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6477832512315271</v>
+        <v>0.6687192118226601</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5911330049261084</v>
+        <v>0.6305418719211823</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5751231527093597</v>
+        <v>0.5800492610837439</v>
       </c>
       <c r="V4" t="n">
         <v>0.4667487684729064</v>
@@ -1317,488 +1509,488 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D5" t="n">
+        <v>0.8990147783251231</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8805418719211823</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.875615763546798</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.8719211822660099</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8472906403940886</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="J5" t="n">
-        <v>0.791871921182266</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.8201970443349754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7697044334975369</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7549261083743842</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7278325123152709</v>
+        <v>0.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7376847290640394</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="S5" t="n">
-        <v>0.645320197044335</v>
+        <v>0.6564039408866995</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5874384236453202</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.895320197044335</v>
       </c>
       <c r="E6" t="n">
-        <v>0.916256157635468</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.8165024630541872</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.7980295566502463</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.7795566502463054</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.7475369458128078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7315270935960592</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="T6" t="n">
-        <v>0.604679802955665</v>
+        <v>0.603448275862069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5369458128078818</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.895320197044335</v>
       </c>
       <c r="E7" t="n">
-        <v>0.916256157635468</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="F7" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="H7" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I7" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8817733990147784</v>
+        <v>0.8165024630541872</v>
       </c>
       <c r="K7" t="n">
-        <v>0.875615763546798</v>
+        <v>0.7980295566502463</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8608374384236454</v>
+        <v>0.7795566502463054</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8226600985221675</v>
+        <v>0.7475369458128078</v>
       </c>
       <c r="O7" t="n">
-        <v>0.812807881773399</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6650246305418719</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.603448275862069</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5443349753694581</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.874384236453202</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8509852216748769</v>
+        <v>0.8399014778325123</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8349753694581281</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8238916256157636</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.7844827586206896</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.7561576354679803</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7943349753694581</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.6945812807881774</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7327586206896551</v>
+        <v>0.6921182266009852</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6564039408866995</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.6219211822660099</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6108374384236454</v>
+        <v>0.5948275862068966</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5591133004926109</v>
+        <v>0.5467980295566502</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="D9" t="n">
-        <v>0.919950738916256</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="K9" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8115763546798029</v>
+        <v>0.7783251231527094</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7660098522167488</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7352216748768473</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6748768472906403</v>
+        <v>0.6810344827586207</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6440886699507389</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5332512315270936</v>
+        <v>0.5775862068965517</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.919950738916256</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="E10" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="F10" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9027093596059114</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="H10" t="n">
-        <v>0.895320197044335</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8731527093596059</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.7955665024630542</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.7684729064039408</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8312807881773399</v>
+        <v>0.7401477832512315</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8054187192118226</v>
+        <v>0.7179802955665024</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7820197044334976</v>
+        <v>0.6847290640394089</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7573891625615764</v>
+        <v>0.6761083743842364</v>
       </c>
       <c r="R10" t="n">
-        <v>0.708128078817734</v>
+        <v>0.6477832512315271</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5997536945812808</v>
+        <v>0.5911330049261084</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.5751231527093597</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="E11" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8312807881773399</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.8300492610837439</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.8103448275862069</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.791871921182266</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="L11" t="n">
+        <v>0.7697044334975369</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.7549261083743842</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7524630541871922</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7278325123152709</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7068965517241379</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0.6970443349753694</v>
       </c>
-      <c r="M11" t="n">
-        <v>0.6834975369458128</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.6773399014778325</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.6625615763546798</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.6502463054187192</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.6182266009852216</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.645320197044335</v>
       </c>
       <c r="T11" t="n">
+        <v>0.6059113300492611</v>
+      </c>
+      <c r="U11" t="n">
         <v>0.5529556650246306</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.5258620689655172</v>
       </c>
       <c r="V11" t="n">
         <v>0.4655172413793103</v>
@@ -1807,68 +1999,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9261083743842364</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9248768472906403</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F12" t="n">
         <v>0.9113300492610836</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8990147783251231</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="K12" t="n">
         <v>0.8633004926108374</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8288177339901478</v>
+        <v>0.8423645320197044</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.8349753694581281</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7967980295566502</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="P12" t="n">
         <v>0.7733990147783252</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7364532019704434</v>
+        <v>0.7315270935960592</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6958128078817734</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5849753694581281</v>
+        <v>0.604679802955665</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5123152709359606</v>
+        <v>0.5369458128078818</v>
       </c>
       <c r="V12" t="n">
         <v>0.4655172413793103</v>
@@ -1877,7 +2069,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1887,55 +2079,55 @@
         <v>0.9088669950738916</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9261083743842364</v>
+        <v>0.9174876847290639</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F13" t="n">
         <v>0.916256157635468</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9039408866995072</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8768472906403941</v>
+        <v>0.8817733990147784</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8608374384236454</v>
       </c>
       <c r="M13" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8362068965517241</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8066502463054187</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7832512315270936</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7598522167487685</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6650246305418719</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6096059113300493</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U13" t="n">
         <v>0.5443349753694581</v>
@@ -1947,68 +2139,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>smoothgrad</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="G14" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8509852216748769</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.8423645320197044</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="L14" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="M14" t="n">
         <v>0.8091133004926109</v>
       </c>
-      <c r="M14" t="n">
-        <v>0.7869458128078818</v>
-      </c>
       <c r="N14" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.7943349753694581</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7118226600985221</v>
+        <v>0.7327586206896551</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6600985221674877</v>
+        <v>0.6958128078817734</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5972906403940886</v>
+        <v>0.6108374384236454</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5566502463054187</v>
+        <v>0.5591133004926109</v>
       </c>
       <c r="V14" t="n">
         <v>0.4655172413793103</v>
@@ -2017,70 +2209,490 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>inputxgradient</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.919950738916256</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9051724137931034</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8977832512315271</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.854679802955665</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8399014778325123</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8115763546798029</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8004926108374384</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.7660098522167488</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.7352216748768473</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.7167487684729064</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.6748768472906403</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6440886699507389</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5874384236453202</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.5332512315270936</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>integrated_gradients</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9051724137931034</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.919950738916256</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9027093596059114</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.895320197044335</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8793103448275862</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8731527093596059</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8633004926108374</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8522167487684729</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8460591133004927</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8312807881773399</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.8054187192118226</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.7820197044334976</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7573891625615764</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.708128078817734</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6514778325123153</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.5997536945812808</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5603448275862069</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>occlusion</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8854679802955665</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8780788177339901</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.854679802955665</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8312807881773399</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8004926108374384</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7807881773399015</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7463054187192119</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7167487684729064</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6970443349753694</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6834975369458128</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6773399014778325</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.6625615763546798</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.6502463054187192</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6182266009852216</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.604679802955665</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.5529556650246306</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5258620689655172</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9261083743842364</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9248768472906403</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8990147783251231</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8854679802955665</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.8633004926108374</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8497536945812808</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8288177339901478</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.8201970443349754</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.7967980295566502</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.7733990147783252</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7364532019704434</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6514778325123153</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.5849753694581281</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.5123152709359606</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9261083743842364</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9174876847290639</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9039408866995072</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9002463054187192</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8768472906403941</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8854679802955665</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8694581280788177</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.854679802955665</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8362068965517241</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8066502463054187</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7832512315270936</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.7598522167487685</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.7204433497536946</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6674876847290641</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.6096059113300493</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5443349753694581</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>smoothgrad</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8916256157635468</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8916256157635468</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.875615763546798</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8694581280788177</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8472906403940886</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8300492610837439</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8201970443349754</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8091133004926109</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.7869458128078818</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7610837438423645</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.7463054187192119</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.7118226600985221</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.6859605911330049</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.6600985221674877</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.6293103448275862</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5972906403940886</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5566502463054187</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B21" t="n">
         <v>0.9064039408866996</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C21" t="n">
         <v>0.915024630541872</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D21" t="n">
         <v>0.9064039408866996</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E21" t="n">
         <v>0.9039408866995072</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F21" t="n">
         <v>0.8854679802955665</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G21" t="n">
         <v>0.8706896551724138</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H21" t="n">
         <v>0.8633004926108374</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I21" t="n">
         <v>0.8435960591133005</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J21" t="n">
         <v>0.8300492610837439</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K21" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L21" t="n">
         <v>0.7820197044334976</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M21" t="n">
         <v>0.7610837438423645</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N21" t="n">
         <v>0.7524630541871922</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O21" t="n">
         <v>0.7401477832512315</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P21" t="n">
         <v>0.7204433497536946</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q21" t="n">
         <v>0.6995073891625616</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R21" t="n">
         <v>0.6834975369458128</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S21" t="n">
         <v>0.6539408866995073</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T21" t="n">
         <v>0.6071428571428571</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U21" t="n">
         <v>0.5480295566502463</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V21" t="n">
         <v>0.4655172413793103</v>
       </c>
     </row>

--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
@@ -784,38 +784,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -889,7 +857,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1199,10 +1167,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1369,68 +1337,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.9064039408866996</v>
       </c>
       <c r="D3" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8866995073891626</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.8842364532019704</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8596059113300493</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8485221674876847</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8226600985221675</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7992610837438424</v>
+        <v>0.8189655172413793</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7549261083743842</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7450738916256158</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7376847290640394</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.687192118226601</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.6687192118226601</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6391625615763546</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="T3" t="n">
-        <v>0.625615763546798</v>
+        <v>0.6305418719211823</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5615763546798029</v>
+        <v>0.5800492610837439</v>
       </c>
       <c r="V3" t="n">
         <v>0.4667487684729064</v>
@@ -1439,68 +1407,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8866995073891626</v>
+        <v>0.8990147783251231</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8805418719211823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8842364532019704</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8485221674876847</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8189655172413793</v>
+        <v>0.8201970443349754</v>
       </c>
       <c r="L4" t="n">
         <v>0.8041871921182266</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7721674876847291</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="O4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.7376847290640394</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.708128078817734</v>
-      </c>
       <c r="Q4" t="n">
-        <v>0.687192118226601</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6687192118226601</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="S4" t="n">
-        <v>0.646551724137931</v>
+        <v>0.6564039408866995</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6305418719211823</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5800492610837439</v>
+        <v>0.5874384236453202</v>
       </c>
       <c r="V4" t="n">
         <v>0.4667487684729064</v>
@@ -1509,68 +1477,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8990147783251231</v>
+        <v>0.895320197044335</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8805418719211823</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8706896551724138</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8386699507389163</v>
+        <v>0.8165024630541872</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.7980295566502463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8041871921182266</v>
+        <v>0.7795566502463054</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.7475369458128078</v>
       </c>
       <c r="O5" t="n">
-        <v>0.75</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7376847290640394</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6564039408866995</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.603448275862069</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="V5" t="n">
         <v>0.4667487684729064</v>
@@ -1579,7 +1547,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1649,68 +1617,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D7" t="n">
-        <v>0.895320197044335</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="E7" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.874384236453202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.8399014778325123</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8349753694581281</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8386699507389163</v>
+        <v>0.8238916256157636</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8165024630541872</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7980295566502463</v>
+        <v>0.7844827586206896</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7795566502463054</v>
+        <v>0.7561576354679803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7721674876847291</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7475369458128078</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="O7" t="n">
-        <v>0.729064039408867</v>
+        <v>0.6945812807881774</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6995073891625616</v>
+        <v>0.6921182266009852</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6564039408866995</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.6219211822660099</v>
       </c>
       <c r="T7" t="n">
-        <v>0.603448275862069</v>
+        <v>0.5948275862068966</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.5467980295566502</v>
       </c>
       <c r="V7" t="n">
         <v>0.4667487684729064</v>
@@ -1719,68 +1687,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F8" t="n">
-        <v>0.874384236453202</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8238916256157636</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7844827586206896</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7561576354679803</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.7783251231527094</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6945812807881774</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6921182266009852</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6564039408866995</v>
+        <v>0.6810344827586207</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6219211822660099</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5948275862068966</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5467980295566502</v>
+        <v>0.5775862068965517</v>
       </c>
       <c r="V8" t="n">
         <v>0.4667487684729064</v>
@@ -1789,68 +1757,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D9" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8263546798029556</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.7955665024630542</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8041871921182266</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7783251231527094</v>
+        <v>0.7684729064039408</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7401477832512315</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7179802955665024</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.6847290640394089</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7093596059113301</v>
+        <v>0.6761083743842364</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6810344827586207</v>
+        <v>0.6477832512315271</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.5911330049261084</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5775862068965517</v>
+        <v>0.5751231527093597</v>
       </c>
       <c r="V9" t="n">
         <v>0.4667487684729064</v>
@@ -1859,138 +1827,138 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F10" t="n">
         <v>0.8472906403940886</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.8300492610837439</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8263546798029556</v>
+        <v>0.8103448275862069</v>
       </c>
       <c r="J10" t="n">
-        <v>0.812807881773399</v>
+        <v>0.791871921182266</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7955665024630542</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.7697044334975369</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7684729064039408</v>
+        <v>0.7549261083743842</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7401477832512315</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7179802955665024</v>
+        <v>0.7278325123152709</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6847290640394089</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6761083743842364</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6477832512315271</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.645320197044335</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5911330049261084</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5751231527093597</v>
+        <v>0.5529556650246306</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4655172413793103</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C11" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D11" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.9113300492610836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="J11" t="n">
-        <v>0.791871921182266</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7697044334975369</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7549261083743842</v>
+        <v>0.8423645320197044</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.8349753694581281</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7278325123152709</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.7315270935960592</v>
       </c>
       <c r="R11" t="n">
+        <v>0.6958128078817734</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.6637931034482759</v>
       </c>
-      <c r="S11" t="n">
-        <v>0.645320197044335</v>
-      </c>
       <c r="T11" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.604679802955665</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5369458128078818</v>
       </c>
       <c r="V11" t="n">
         <v>0.4655172413793103</v>
@@ -1999,7 +1967,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2009,58 +1977,58 @@
         <v>0.9088669950738916</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9174876847290639</v>
       </c>
       <c r="E12" t="n">
         <v>0.916256157635468</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.8817733990147784</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8608374384236454</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7315270935960592</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6650246305418719</v>
       </c>
       <c r="T12" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5369458128078818</v>
+        <v>0.5443349753694581</v>
       </c>
       <c r="V12" t="n">
         <v>0.4655172413793103</v>
@@ -2069,68 +2037,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="E13" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="F13" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8509852216748769</v>
       </c>
       <c r="H13" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="I13" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8817733990147784</v>
+        <v>0.8423645320197044</v>
       </c>
       <c r="K13" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8608374384236454</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.8091133004926109</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8226600985221675</v>
+        <v>0.7943349753694581</v>
       </c>
       <c r="O13" t="n">
-        <v>0.812807881773399</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.7327586206896551</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.6958128078817734</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6650246305418719</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.6108374384236454</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5443349753694581</v>
+        <v>0.5591133004926109</v>
       </c>
       <c r="V13" t="n">
         <v>0.4655172413793103</v>
@@ -2139,68 +2107,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C14" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.919950738916256</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9051724137931034</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.8977832512315271</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.8780788177339901</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.8694581280788177</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8669950738916257</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.8509852216748769</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.8522167487684729</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8399014778325123</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.8115763546798029</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7943349753694581</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.7660098522167488</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7327586206896551</v>
+        <v>0.7352216748768473</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6748768472906403</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.6440886699507389</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6108374384236454</v>
+        <v>0.5874384236453202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5591133004926109</v>
+        <v>0.5332512315270936</v>
       </c>
       <c r="V14" t="n">
         <v>0.4655172413793103</v>
@@ -2209,68 +2177,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="D15" t="n">
         <v>0.919950738916256</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.9027093596059114</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.895320197044335</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8731527093596059</v>
       </c>
       <c r="K15" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8115763546798029</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7660098522167488</v>
+        <v>0.8054187192118226</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7352216748768473</v>
+        <v>0.7820197044334976</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7573891625615764</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6748768472906403</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6440886699507389</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.5997536945812808</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5332512315270936</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="V15" t="n">
         <v>0.4655172413793103</v>
@@ -2279,68 +2247,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="D16" t="n">
-        <v>0.919950738916256</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="E16" t="n">
-        <v>0.916256157635468</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="F16" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9027093596059114</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="H16" t="n">
-        <v>0.895320197044335</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8731527093596059</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.6834975369458128</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8312807881773399</v>
+        <v>0.6773399014778325</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8054187192118226</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7820197044334976</v>
+        <v>0.6502463054187192</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7573891625615764</v>
+        <v>0.6182266009852216</v>
       </c>
       <c r="R16" t="n">
-        <v>0.708128078817734</v>
+        <v>0.604679802955665</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5997536945812808</v>
+        <v>0.5529556650246306</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.5258620689655172</v>
       </c>
       <c r="V16" t="n">
         <v>0.4655172413793103</v>
@@ -2349,68 +2317,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C17" t="n">
+        <v>0.9064039408866996</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9261083743842364</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9248768472906403</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8990147783251231</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.8854679802955665</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.8780788177339901</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.854679802955665</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.8312807881773399</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.8004926108374384</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.7807881773399015</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.7463054187192119</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.7241379310344828</v>
-      </c>
       <c r="K17" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6834975369458128</v>
+        <v>0.8288177339901478</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6773399014778325</v>
+        <v>0.8201970443349754</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.7967980295566502</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6502463054187192</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6182266009852216</v>
+        <v>0.7364532019704434</v>
       </c>
       <c r="R17" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5849753694581281</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5258620689655172</v>
+        <v>0.5123152709359606</v>
       </c>
       <c r="V17" t="n">
         <v>0.4655172413793103</v>
@@ -2419,68 +2387,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D18" t="n">
         <v>0.9261083743842364</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9248768472906403</v>
+        <v>0.9174876847290639</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9039408866995072</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8990147783251231</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="J18" t="n">
+        <v>0.8768472906403941</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.8854679802955665</v>
       </c>
-      <c r="K18" t="n">
-        <v>0.8633004926108374</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8288177339901478</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.8362068965517241</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7967980295566502</v>
+        <v>0.8066502463054187</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7832512315270936</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7364532019704434</v>
+        <v>0.7598522167487685</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6674876847290641</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5849753694581281</v>
+        <v>0.6096059113300493</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5123152709359606</v>
+        <v>0.5443349753694581</v>
       </c>
       <c r="V18" t="n">
         <v>0.4655172413793103</v>
@@ -2489,68 +2457,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>smoothgrad</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9064039408866996</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9261083743842364</v>
+        <v>0.8916256157635468</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.8916256157635468</v>
       </c>
       <c r="F19" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9039408866995072</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8768472906403941</v>
+        <v>0.8300492610837439</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8201970443349754</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8091133004926109</v>
       </c>
       <c r="M19" t="n">
-        <v>0.854679802955665</v>
+        <v>0.7869458128078818</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8362068965517241</v>
+        <v>0.7610837438423645</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8066502463054187</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7832512315270936</v>
+        <v>0.7118226600985221</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7598522167487685</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.6600985221674877</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6293103448275862</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6096059113300493</v>
+        <v>0.5972906403940886</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5443349753694581</v>
+        <v>0.5566502463054187</v>
       </c>
       <c r="V19" t="n">
         <v>0.4655172413793103</v>
@@ -2559,140 +2527,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>smoothgrad</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C20" t="n">
+        <v>0.915024630541872</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.9064039408866996</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.8916256157635468</v>
-      </c>
       <c r="E20" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.9039408866995072</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="G20" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8435960591133005</v>
       </c>
       <c r="J20" t="n">
         <v>0.8300492610837439</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.7820197044334976</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7869458128078818</v>
+        <v>0.7610837438423645</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.7401477832512315</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7118226600985221</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6600985221674877</v>
+        <v>0.6834975369458128</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.6539408866995073</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5972906403940886</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5566502463054187</v>
+        <v>0.5480295566502463</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4655172413793103</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.915024630541872</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.9039408866995072</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.8854679802955665</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.8706896551724138</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.8633004926108374</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.8435960591133005</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.8300492610837439</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7931034482758621</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.7820197044334976</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7610837438423645</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.7524630541871922</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.7401477832512315</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.7204433497536946</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.6995073891625616</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.6834975369458128</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.6539408866995073</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.5480295566502463</v>
-      </c>
-      <c r="V21" t="n">
         <v>0.4655172413793103</v>
       </c>
     </row>

--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
@@ -1267,138 +1267,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8768472906403941</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8731527093596059</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8682266009852216</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.833743842364532</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8238916256157636</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8017241379310345</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="L2" t="n">
-        <v>0.770935960591133</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7512315270935961</v>
+        <v>0.6834975369458128</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7339901477832512</v>
+        <v>0.6773399014778325</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7130541871921182</v>
+        <v>0.6502463054187192</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.6182266009852216</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6711822660098522</v>
+        <v>0.604679802955665</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6477832512315271</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6083743842364532</v>
+        <v>0.5529556650246306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5578817733990148</v>
+        <v>0.5258620689655172</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4655172413793103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8866995073891626</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8842364532019704</v>
+        <v>0.874384236453202</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8399014778325123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.8349753694581281</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8485221674876847</v>
+        <v>0.8238916256157636</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8189655172413793</v>
+        <v>0.7844827586206896</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8041871921182266</v>
+        <v>0.7561576354679803</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7721674876847291</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7376847290640394</v>
+        <v>0.6945812807881774</v>
       </c>
       <c r="P3" t="n">
-        <v>0.708128078817734</v>
+        <v>0.6921182266009852</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.687192118226601</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6687192118226601</v>
+        <v>0.6564039408866995</v>
       </c>
       <c r="S3" t="n">
-        <v>0.646551724137931</v>
+        <v>0.6219211822660099</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6305418719211823</v>
+        <v>0.5948275862068966</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5800492610837439</v>
+        <v>0.5467980295566502</v>
       </c>
       <c r="V3" t="n">
         <v>0.4667487684729064</v>
@@ -1407,7 +1407,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1417,58 +1417,58 @@
         <v>0.8977832512315271</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8990147783251231</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8805418719211823</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="F4" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8706896551724138</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8386699507389163</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.7955665024630542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8041871921182266</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7684729064039408</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.7401477832512315</v>
       </c>
       <c r="O4" t="n">
-        <v>0.75</v>
+        <v>0.7179802955665024</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7376847290640394</v>
+        <v>0.6847290640394089</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6761083743842364</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.6477832512315271</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6564039408866995</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.5911330049261084</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.5751231527093597</v>
       </c>
       <c r="V4" t="n">
         <v>0.4667487684729064</v>
@@ -1617,138 +1617,138 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>smoothgrad</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9064039408866996</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8916256157635468</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8916256157635468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.874384236453202</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8238916256157636</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.8300492610837439</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7844827586206896</v>
+        <v>0.8201970443349754</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7561576354679803</v>
+        <v>0.8091133004926109</v>
       </c>
       <c r="M7" t="n">
+        <v>0.7869458128078818</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7610837438423645</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.7463054187192119</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.7167487684729064</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6945812807881774</v>
-      </c>
       <c r="P7" t="n">
-        <v>0.6921182266009852</v>
+        <v>0.7118226600985221</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6564039408866995</v>
+        <v>0.6600985221674877</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6219211822660099</v>
+        <v>0.6293103448275862</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5948275862068966</v>
+        <v>0.5972906403940886</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5467980295566502</v>
+        <v>0.5566502463054187</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4655172413793103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.9064039408866996</v>
       </c>
       <c r="D8" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8866995073891626</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8842364532019704</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="I8" t="n">
+        <v>0.8485221674876847</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.8472906403940886</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.8263546798029556</v>
-      </c>
       <c r="K8" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8189655172413793</v>
       </c>
       <c r="L8" t="n">
         <v>0.8041871921182266</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7783251231527094</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7376847290640394</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7093596059113301</v>
+        <v>0.687192118226601</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6810344827586207</v>
+        <v>0.6687192118226601</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.6305418719211823</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5775862068965517</v>
+        <v>0.5800492610837439</v>
       </c>
       <c r="V8" t="n">
         <v>0.4667487684729064</v>
@@ -1757,138 +1757,138 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F9" t="n">
         <v>0.8472906403940886</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.8300492610837439</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8263546798029556</v>
+        <v>0.8103448275862069</v>
       </c>
       <c r="J9" t="n">
-        <v>0.812807881773399</v>
+        <v>0.791871921182266</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7955665024630542</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.7697044334975369</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7684729064039408</v>
+        <v>0.7549261083743842</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7401477832512315</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7179802955665024</v>
+        <v>0.7278325123152709</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6847290640394089</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6761083743842364</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6477832512315271</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.645320197044335</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5911330049261084</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5751231527093597</v>
+        <v>0.5529556650246306</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4655172413793103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.896551724137931</v>
+        <v>0.915024630541872</v>
       </c>
       <c r="D10" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9064039408866996</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.9039408866995072</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8854679802955665</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="H10" t="n">
+        <v>0.8633004926108374</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8435960591133005</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.8300492610837439</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.8103448275862069</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.791871921182266</v>
-      </c>
       <c r="K10" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7697044334975369</v>
+        <v>0.7820197044334976</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7549261083743842</v>
+        <v>0.7610837438423645</v>
       </c>
       <c r="N10" t="n">
         <v>0.7524630541871922</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7278325123152709</v>
+        <v>0.7401477832512315</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6834975369458128</v>
       </c>
       <c r="S10" t="n">
-        <v>0.645320197044335</v>
+        <v>0.6539408866995073</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5480295566502463</v>
       </c>
       <c r="V10" t="n">
         <v>0.4655172413793103</v>
@@ -1897,208 +1897,208 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>c3f</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.8768472906403941</v>
       </c>
       <c r="E11" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8731527093596059</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.8682266009852216</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.833743842364532</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.8238916256157636</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.8017241379310345</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.770935960591133</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.7512315270935961</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.7339901477832512</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7130541871921182</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7315270935960592</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6711822660098522</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.6477832512315271</v>
       </c>
       <c r="T11" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6083743842364532</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5369458128078818</v>
+        <v>0.5578817733990148</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9002463054187192</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E12" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="F12" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="H12" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="I12" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8817733990147784</v>
+        <v>0.8263546798029556</v>
       </c>
       <c r="K12" t="n">
-        <v>0.875615763546798</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8608374384236454</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.7783251231527094</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8226600985221675</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="O12" t="n">
-        <v>0.812807881773399</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.6810344827586207</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6650246305418719</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.6194581280788177</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5443349753694581</v>
+        <v>0.5775862068965517</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C13" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.919950738916256</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9051724137931034</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8891625615763546</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.8977832512315271</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.8780788177339901</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.8694581280788177</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8669950738916257</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.8509852216748769</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8522167487684729</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8399014778325123</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.8115763546798029</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7943349753694581</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.7660098522167488</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7327586206896551</v>
+        <v>0.7352216748768473</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7167487684729064</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.6748768472906403</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.6440886699507389</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6108374384236454</v>
+        <v>0.5874384236453202</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5591133004926109</v>
+        <v>0.5332512315270936</v>
       </c>
       <c r="V13" t="n">
         <v>0.4655172413793103</v>
@@ -2107,68 +2107,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D14" t="n">
-        <v>0.919950738916256</v>
+        <v>0.8780788177339901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.8509852216748769</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8423645320197044</v>
       </c>
       <c r="K14" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8115763546798029</v>
+        <v>0.8091133004926109</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.7943349753694581</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7660098522167488</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7352216748768473</v>
+        <v>0.7327586206896551</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6748768472906403</v>
+        <v>0.6958128078817734</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6440886699507389</v>
+        <v>0.6625615763546798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.6108374384236454</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5332512315270936</v>
+        <v>0.5591133004926109</v>
       </c>
       <c r="V14" t="n">
         <v>0.4655172413793103</v>
@@ -2177,138 +2177,138 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="D15" t="n">
-        <v>0.919950738916256</v>
+        <v>0.8990147783251231</v>
       </c>
       <c r="E15" t="n">
-        <v>0.916256157635468</v>
+        <v>0.8805418719211823</v>
       </c>
       <c r="F15" t="n">
-        <v>0.916256157635468</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9027093596059114</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="H15" t="n">
-        <v>0.895320197044335</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.8497536945812808</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8731527093596059</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.8201970443349754</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8041871921182266</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8312807881773399</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8054187192118226</v>
+        <v>0.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7820197044334976</v>
+        <v>0.7376847290640394</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7573891625615764</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="R15" t="n">
-        <v>0.708128078817734</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6564039408866995</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5997536945812808</v>
+        <v>0.6317733990147784</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.5874384236453202</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4667487684729064</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C16" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9088669950738916</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9113300492610836</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9002463054187192</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8903940886699507</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.8854679802955665</v>
       </c>
-      <c r="D16" t="n">
+      <c r="J16" t="n">
         <v>0.8780788177339901</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.854679802955665</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.8312807881773399</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="K16" t="n">
+        <v>0.8633004926108374</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8583743842364532</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8423645320197044</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8349753694581281</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.8004926108374384</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.7807881773399015</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.7463054187192119</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.7241379310344828</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.7167487684729064</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.6970443349753694</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.6834975369458128</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.6773399014778325</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6625615763546798</v>
-      </c>
       <c r="P16" t="n">
-        <v>0.6502463054187192</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6182266009852216</v>
+        <v>0.7315270935960592</v>
       </c>
       <c r="R16" t="n">
+        <v>0.6958128078817734</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6637931034482759</v>
+      </c>
+      <c r="T16" t="n">
         <v>0.604679802955665</v>
       </c>
-      <c r="S16" t="n">
-        <v>0.5862068965517241</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.5529556650246306</v>
-      </c>
       <c r="U16" t="n">
-        <v>0.5258620689655172</v>
+        <v>0.5369458128078818</v>
       </c>
       <c r="V16" t="n">
         <v>0.4655172413793103</v>
@@ -2387,7 +2387,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2397,55 +2397,55 @@
         <v>0.9088669950738916</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9261083743842364</v>
+        <v>0.9174876847290639</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9174876847290639</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F18" t="n">
         <v>0.916256157635468</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9039408866995072</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8768472906403941</v>
+        <v>0.8817733990147784</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.875615763546798</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.8608374384236454</v>
       </c>
       <c r="M18" t="n">
-        <v>0.854679802955665</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8362068965517241</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8066502463054187</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7832512315270936</v>
+        <v>0.7906403940886699</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7598522167487685</v>
+        <v>0.7524630541871922</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.7032019704433498</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6650246305418719</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6096059113300493</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="U18" t="n">
         <v>0.5443349753694581</v>
@@ -2457,68 +2457,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>smoothgrad</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.919950738916256</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="G19" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9027093596059114</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.895320197044335</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.8731527093596059</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.8522167487684729</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7869458128078818</v>
+        <v>0.8460591133004927</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.8054187192118226</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7118226600985221</v>
+        <v>0.7820197044334976</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.7573891625615764</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6600985221674877</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5972906403940886</v>
+        <v>0.5997536945812808</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5566502463054187</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="V19" t="n">
         <v>0.4655172413793103</v>
@@ -2527,74 +2527,86 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>xrai</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.9064039408866996</v>
       </c>
       <c r="C20" t="n">
-        <v>0.915024630541872</v>
+        <v>0.9088669950738916</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9261083743842364</v>
       </c>
       <c r="E20" t="n">
+        <v>0.9174876847290639</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.9039408866995072</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
+        <v>0.9002463054187192</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8768472906403941</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.8854679802955665</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.8706896551724138</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.8633004926108374</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.8435960591133005</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.8300492610837439</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.7931034482758621</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.7820197044334976</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.8362068965517241</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7401477832512315</v>
+        <v>0.8066502463054187</v>
       </c>
       <c r="P20" t="n">
+        <v>0.7832512315270936</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.7598522167487685</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.7204433497536946</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.6995073891625616</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.6834975369458128</v>
-      </c>
       <c r="S20" t="n">
-        <v>0.6539408866995073</v>
+        <v>0.6674876847290641</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.6096059113300493</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5480295566502463</v>
+        <v>0.5443349753694581</v>
       </c>
       <c r="V20" t="n">
         <v>0.4655172413793103</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:V20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_sipakmed_cropped_ResNet50.pth_blur.xlsx
@@ -656,134 +656,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="15"/>
-          <order val="15"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$17:$V$17</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="16"/>
-          <order val="16"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A18</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$18:$V$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="17"/>
-          <order val="17"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A19</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$19:$V$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="18"/>
-          <order val="18"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A20</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$20:$V$20</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -857,7 +729,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1167,10 +1039,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1190,8 +1062,8 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1271,1331 +1143,1051 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.9593596059113301</v>
       </c>
       <c r="D2" t="n">
+        <v>0.9507389162561576</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9322660098522167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9064039408866995</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.8780788177339901</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.854679802955665</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.8312807881773399</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8004926108374384</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.7807881773399015</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.853448275862069</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.8251231527093597</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.8054187192118226</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.7881773399014779</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6834975369458128</v>
+        <v>0.7426108374384236</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6773399014778325</v>
+        <v>0.7105911330049262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.6958128078817734</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6502463054187192</v>
+        <v>0.6736453201970444</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6182266009852216</v>
+        <v>0.6588669950738916</v>
       </c>
       <c r="R2" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6268472906403941</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6083743842364532</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5726600985221675</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5258620689655172</v>
+        <v>0.5369458128078818</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.958128078817734</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.9519704433497537</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.9421182266009852</v>
       </c>
       <c r="F3" t="n">
-        <v>0.874384236453202</v>
+        <v>0.9236453201970444</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8399014778325123</v>
+        <v>0.9174876847290641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8238916256157636</v>
+        <v>0.8657635467980296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7906403940886699</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7844827586206896</v>
+        <v>0.8115763546798029</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7561576354679803</v>
+        <v>0.7795566502463054</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.7610837438423645</v>
       </c>
       <c r="N3" t="n">
+        <v>0.7364532019704434</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.7167487684729064</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.6945812807881774</v>
-      </c>
       <c r="P3" t="n">
-        <v>0.6921182266009852</v>
+        <v>0.7007389162561576</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6625615763546798</v>
+        <v>0.6810344827586207</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6564039408866995</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6219211822660099</v>
+        <v>0.666256157635468</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5948275862068966</v>
+        <v>0.6440886699507389</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5467980295566502</v>
+        <v>0.6059113300492611</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.9519704433497537</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.9519704433497537</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.9458128078817734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.9433497536945813</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8460591133004927</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.9187192118226601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8263546798029556</v>
+        <v>0.9076354679802956</v>
       </c>
       <c r="J4" t="n">
-        <v>0.812807881773399</v>
+        <v>0.8830049261083743</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7955665024630542</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7807881773399015</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7684729064039408</v>
+        <v>0.8288177339901478</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7401477832512315</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7179802955665024</v>
+        <v>0.791871921182266</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6847290640394089</v>
+        <v>0.7327586206896551</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6761083743842364</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6477832512315271</v>
+        <v>0.6970443349753694</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.6576354679802956</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5911330049261084</v>
+        <v>0.625615763546798</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5751231527093597</v>
+        <v>0.5578817733990148</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.9384236453201971</v>
       </c>
       <c r="D5" t="n">
-        <v>0.895320197044335</v>
+        <v>0.9359605911330049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9211822660098522</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.9113300492610837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.8990147783251231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8940886699507389</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8386699507389163</v>
+        <v>0.8866995073891626</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8165024630541872</v>
+        <v>0.8768472906403941</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7980295566502463</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7795566502463054</v>
+        <v>0.8657635467980296</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7721674876847291</v>
+        <v>0.8411330049261084</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7475369458128078</v>
+        <v>0.8312807881773399</v>
       </c>
       <c r="O5" t="n">
-        <v>0.729064039408867</v>
+        <v>0.7967980295566502</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6995073891625616</v>
+        <v>0.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.708128078817734</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6761083743842364</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.6169950738916257</v>
       </c>
       <c r="T5" t="n">
-        <v>0.603448275862069</v>
+        <v>0.5554187192118226</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.5036945812807881</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>u2net_dino_fusion</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9051724137931034</v>
+        <v>0.958128078817734</v>
       </c>
       <c r="D6" t="n">
-        <v>0.895320197044335</v>
+        <v>0.9630541871921182</v>
       </c>
       <c r="E6" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9630541871921182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.958128078817734</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.9458128078817734</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8386699507389163</v>
+        <v>0.9113300492610837</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8165024630541872</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7980295566502463</v>
+        <v>0.8645320197044335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7795566502463054</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7721674876847291</v>
+        <v>0.8140394088669951</v>
       </c>
       <c r="N6" t="n">
+        <v>0.7746305418719212</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.7475369458128078</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.729064039408867</v>
-      </c>
       <c r="P6" t="n">
+        <v>0.7167487684729064</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7167487684729064</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.6995073891625616</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.6724137931034483</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.6736453201970444</v>
       </c>
       <c r="T6" t="n">
-        <v>0.603448275862069</v>
+        <v>0.6576354679802956</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5603448275862069</v>
+        <v>0.6330049261083743</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>smoothgrad</t>
+          <t>u2net_dino_product</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9568965517241379</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8916256157635468</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.9495073891625616</v>
       </c>
       <c r="G7" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9458128078817734</v>
       </c>
       <c r="H7" t="n">
+        <v>0.9396551724137931</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.916256157635468</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8879310344827587</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.8694581280788177</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.8472906403940886</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8300492610837439</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>0.8460591133004927</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.8201970443349754</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.8091133004926109</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.7869458128078818</v>
-      </c>
       <c r="N7" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.7807881773399015</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7463054187192119</v>
+        <v>0.7549261083743842</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7118226600985221</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.7179802955665024</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6600985221674877</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.6724137931034483</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5972906403940886</v>
+        <v>0.6613300492610837</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5566502463054187</v>
+        <v>0.6342364532019704</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9495073891625616</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8866995073891626</v>
+        <v>0.9544334975369458</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8891625615763546</v>
+        <v>0.9495073891625616</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8842364532019704</v>
+        <v>0.9433497536945813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.9310344827586207</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8559113300492611</v>
+        <v>0.9150246305418719</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8485221674876847</v>
+        <v>0.9014778325123153</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.8940886699507389</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8189655172413793</v>
+        <v>0.8830049261083743</v>
       </c>
       <c r="L8" t="n">
+        <v>0.8657635467980296</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8460591133004927</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8226600985221675</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.8041871921182266</v>
       </c>
-      <c r="M8" t="n">
-        <v>0.7721674876847291</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.7586206896551724</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.7376847290640394</v>
-      </c>
       <c r="P8" t="n">
-        <v>0.708128078817734</v>
+        <v>0.7647783251231527</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.687192118226601</v>
+        <v>0.7487684729064039</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6687192118226601</v>
+        <v>0.7105911330049262</v>
       </c>
       <c r="S8" t="n">
-        <v>0.646551724137931</v>
+        <v>0.6650246305418719</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6305418719211823</v>
+        <v>0.6120689655172413</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5800492610837439</v>
+        <v>0.5480295566502463</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C9" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9421182266009852</v>
       </c>
       <c r="D9" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9396551724137931</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.9347290640394089</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8472906403940886</v>
+        <v>0.9298029556650246</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.9113300492610837</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.8817733990147784</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="J9" t="n">
-        <v>0.791871921182266</v>
+        <v>0.8830049261083743</v>
       </c>
       <c r="K9" t="n">
+        <v>0.874384236453202</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8583743842364532</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8435960591133005</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8312807881773399</v>
+      </c>
+      <c r="P9" t="n">
         <v>0.7906403940886699</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.7697044334975369</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.7549261083743842</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.7524630541871922</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.7278325123152709</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.7068965517241379</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.6970443349753694</v>
+        <v>0.7561576354679803</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.7105911330049262</v>
       </c>
       <c r="S9" t="n">
-        <v>0.645320197044335</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6059113300492611</v>
+        <v>0.5738916256157636</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5529556650246306</v>
+        <v>0.5049261083743842</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xrai</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C10" t="n">
-        <v>0.915024630541872</v>
+        <v>0.9605911330049262</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9039408866995072</v>
+        <v>0.9507389162561576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.937192118226601</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8706896551724138</v>
+        <v>0.9248768472906403</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.9322660098522167</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8435960591133005</v>
+        <v>0.9150246305418719</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8879310344827587</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7820197044334976</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7610837438423645</v>
+        <v>0.8374384236453202</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.8177339901477833</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7401477832512315</v>
+        <v>0.8103448275862069</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7204433497536946</v>
+        <v>0.7746305418719212</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6995073891625616</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6834975369458128</v>
+        <v>0.7364532019704434</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6539408866995073</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.6490147783251231</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5480295566502463</v>
+        <v>0.5763546798029556</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.937192118226601</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8768472906403941</v>
+        <v>0.9334975369458128</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8731527093596059</v>
+        <v>0.9322660098522167</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8682266009852216</v>
+        <v>0.916256157635468</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.9064039408866995</v>
       </c>
       <c r="H11" t="n">
-        <v>0.833743842364532</v>
+        <v>0.9014778325123153</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8238916256157636</v>
+        <v>0.8977832512315271</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.8866995073891626</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8017241379310345</v>
+        <v>0.8805418719211823</v>
       </c>
       <c r="L11" t="n">
-        <v>0.770935960591133</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7512315270935961</v>
+        <v>0.8633004926108374</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7339901477832512</v>
+        <v>0.8559113300492611</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7130541871921182</v>
+        <v>0.8066502463054187</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7032019704433498</v>
+        <v>0.7598522167487685</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6711822660098522</v>
+        <v>0.7192118226600985</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6477832512315271</v>
+        <v>0.6514778325123153</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6083743842364532</v>
+        <v>0.5849753694581281</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5578817733990148</v>
+        <v>0.5024630541871922</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>U2Net-Saliency</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.9605911330049262</v>
       </c>
       <c r="D12" t="n">
-        <v>0.896551724137931</v>
+        <v>0.958128078817734</v>
       </c>
       <c r="E12" t="n">
+        <v>0.9519704433497537</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.958128078817734</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9532019704433498</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9433497536945813</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9359605911330049</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9076354679802956</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.9076354679802956</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.8719211822660099</v>
       </c>
-      <c r="F12" t="n">
+      <c r="M12" t="n">
         <v>0.8583743842364532</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.8522167487684729</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.8497536945812808</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.8472906403940886</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.8263546798029556</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.8275862068965517</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.8041871921182266</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.7783251231527094</v>
-      </c>
       <c r="N12" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7524630541871922</v>
+        <v>0.8078817733990148</v>
       </c>
       <c r="P12" t="n">
+        <v>0.7894088669950738</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7647783251231527</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.7204433497536946</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0.7093596059113301</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.6810344827586207</v>
-      </c>
       <c r="S12" t="n">
-        <v>0.6514778325123153</v>
+        <v>0.6859605911330049</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6194581280788177</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5775862068965517</v>
+        <v>0.6108374384236454</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C13" t="n">
+        <v>0.9408866995073891</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9298029556650246</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9199507389162561</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9113300492610837</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.9088669950738916</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.919950738916256</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.9113300492610836</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9051724137931034</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.8891625615763546</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.8990147783251231</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="J13" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8830049261083743</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8830049261083743</v>
+      </c>
+      <c r="M13" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="K13" t="n">
-        <v>0.854679802955665</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.8399014778325123</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.8115763546798029</v>
-      </c>
       <c r="N13" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.8472906403940886</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7660098522167488</v>
+        <v>0.8349753694581281</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7352216748768473</v>
+        <v>0.8017241379310345</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7167487684729064</v>
+        <v>0.7684729064039408</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6748768472906403</v>
+        <v>0.7204433497536946</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6440886699507389</v>
+        <v>0.6539408866995073</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.5775862068965517</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5332512315270936</v>
+        <v>0.5110837438423645</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.9384236453201971</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.9396551724137931</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8694581280788177</v>
+        <v>0.9298029556650246</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8669950738916257</v>
+        <v>0.9100985221674877</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8509852216748769</v>
+        <v>0.8903940886699507</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8916256157635468</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8522167487684729</v>
+        <v>0.8866995073891626</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8325123152709359</v>
+        <v>0.8682266009852216</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8091133004926109</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7943349753694581</v>
+        <v>0.8386699507389163</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.8226600985221675</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7327586206896551</v>
+        <v>0.8004926108374384</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.770935960591133</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.7266009852216748</v>
       </c>
       <c r="S14" t="n">
         <v>0.6625615763546798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6108374384236454</v>
+        <v>0.5431034482758621</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5591133004926109</v>
+        <v>0.4704433497536946</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8977832512315271</v>
+        <v>0.9334975369458128</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8990147783251231</v>
+        <v>0.9408866995073891</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8805418719211823</v>
+        <v>0.9199507389162561</v>
       </c>
       <c r="F15" t="n">
-        <v>0.875615763546798</v>
+        <v>0.9211822660098522</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8706896551724138</v>
+        <v>0.9051724137931034</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8940886699507389</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8497536945812808</v>
+        <v>0.8891625615763546</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8386699507389163</v>
+        <v>0.8817733990147784</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8201970443349754</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8041871921182266</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8485221674876847</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7746305418719212</v>
+        <v>0.8435960591133005</v>
       </c>
       <c r="O15" t="n">
-        <v>0.75</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7376847290640394</v>
+        <v>0.7980295566502463</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7721674876847291</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6859605911330049</v>
+        <v>0.7229064039408867</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6564039408866995</v>
+        <v>0.6576354679802956</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6317733990147784</v>
+        <v>0.5701970443349754</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5874384236453202</v>
+        <v>0.5049261083743842</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4667487684729064</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9064039408866996</v>
+        <v>0.9556650246305419</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.958128078817734</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9088669950738916</v>
+        <v>0.9495073891625616</v>
       </c>
       <c r="E16" t="n">
-        <v>0.916256157635468</v>
+        <v>0.9384236453201971</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9113300492610836</v>
+        <v>0.9359605911330049</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9002463054187192</v>
+        <v>0.9199507389162561</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8903940886699507</v>
+        <v>0.9076354679802956</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8854679802955665</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8780788177339901</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8633004926108374</v>
+        <v>0.8842364532019704</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8583743842364532</v>
+        <v>0.8682266009852216</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8423645320197044</v>
+        <v>0.8669950738916257</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8349753694581281</v>
+        <v>0.854679802955665</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8004926108374384</v>
+        <v>0.8325123152709359</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7992610837438424</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7315270935960592</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6958128078817734</v>
+        <v>0.7463054187192119</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.7105911330049262</v>
       </c>
       <c r="T16" t="n">
-        <v>0.604679802955665</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5369458128078818</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4655172413793103</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>random_baseline</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.9261083743842364</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9248768472906403</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9113300492610836</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9088669950738916</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.8990147783251231</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8891625615763546</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8854679802955665</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.8633004926108374</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.8497536945812808</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.8288177339901478</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.8201970443349754</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.7967980295566502</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.7733990147783252</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.7364532019704434</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.6896551724137931</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.6514778325123153</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.5849753694581281</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.5123152709359606</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.4655172413793103</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>guided_backprop</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.9088669950738916</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.9174876847290639</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.916256157635468</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.916256157635468</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.9051724137931034</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.896551724137931</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.896551724137931</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8817733990147784</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.875615763546798</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.8608374384236454</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.8559113300492611</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.8226600985221675</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.812807881773399</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.7906403940886699</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.7524630541871922</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.7032019704433498</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.6650246305418719</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.6059113300492611</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.5443349753694581</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.4655172413793103</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>integrated_gradients</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.9051724137931034</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.919950738916256</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.916256157635468</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.916256157635468</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.9027093596059114</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.895320197044335</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.8793103448275862</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.8731527093596059</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8633004926108374</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.8522167487684729</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.8460591133004927</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.8312807881773399</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.8054187192118226</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.7820197044334976</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7573891625615764</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.708128078817734</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.6514778325123153</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.5997536945812808</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.5603448275862069</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.4655172413793103</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>saliency</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.9064039408866996</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.9088669950738916</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.9261083743842364</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9174876847290639</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.916256157635468</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.9039408866995072</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.9002463054187192</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.8768472906403941</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8854679802955665</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.8694581280788177</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.854679802955665</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.8362068965517241</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.8066502463054187</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.7832512315270936</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.7598522167487685</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.7204433497536946</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.6674876847290641</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.6096059113300493</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.5443349753694581</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4507389162561576</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V20">
+  <conditionalFormatting sqref="B2:V16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
